--- a/proposal/创智汇年度活动运营方案-融合版.xlsx
+++ b/proposal/创智汇年度活动运营方案-融合版.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-活动概况" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-定义核资源导入" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-六大主题" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-主体口径收费" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-主体口径与模板说明" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -48,12 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E4D8C"/>
+        <fgColor rgb="001E3A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2F8"/>
+        <fgColor rgb="00F2F0EA"/>
       </patternFill>
     </fill>
   </fills>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -468,11 +468,10 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -508,25 +507,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>场地</t>
+          <t>层次</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>层次</t>
+          <t>招商落点</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>招商落点</t>
+          <t>行程</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>行程</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>嘉宾</t>
         </is>
@@ -565,27 +559,22 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>5F+3F</t>
+          <t>L0</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>L0</t>
+          <t>中介渠道带看与项目推介</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中介渠道带看与项目推介</t>
+          <t>项目介绍→空间导览→政策要点→洽谈→建群</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>项目介绍→空间导览→政策要点→一对一洽谈→建群</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>房产/产业中介、渠道、园区招商</t>
+          <t>中介/渠道/园区招商</t>
         </is>
       </c>
     </row>
@@ -622,27 +611,22 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>5F沙龙</t>
+          <t>L0</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>L0</t>
+          <t>金融资源链接与客户导入</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>金融资源链接与客户导入</t>
+          <t>项目路演→金融对接→座谈→看场→建群</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>项目路演→金融产品对接→需求座谈→看场→建群</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>五大行及合作金融机构对公/科创条线</t>
+          <t>五大行及合作金融机构</t>
         </is>
       </c>
     </row>
@@ -679,27 +663,22 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5F圆桌</t>
+          <t>L0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>L0</t>
+          <t>投研视角放大项目影响力</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>投研视角放大项目影响力</t>
+          <t>定位→赛道研判→圆桌→看场→建群</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>项目定位→产业赛道研判→圆桌→看场→建群</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>券商研究所、产业研究院、智库</t>
+          <t>券商研究所/产业研究院/智库</t>
         </is>
       </c>
     </row>
@@ -736,27 +715,22 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>3F+5F</t>
+          <t>L0</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>L0</t>
+          <t>政策与载体协同落地</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>政策与载体协同落地</t>
+          <t>载体介绍→政策协同→云创资源→看场→建群</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>载体介绍→政策协同→云创基地资源→看场→建群</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>区相关部门、载体、云创基地、服中心</t>
+          <t>区部门/载体/云创/服中心</t>
         </is>
       </c>
     </row>
@@ -793,27 +767,22 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3F+5F</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>衔接WAIC议题与园区看场</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>衔接WAIC议题与园区看场</t>
+          <t>议题速递→园区承接→双展台→洽谈→建群</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>WAIC议题速递→园区承接→双展台→洽谈→建群</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>AI/内容企业、媒体、云创基地代表</t>
+          <t>AI/内容企业、媒体、云创</t>
         </is>
       </c>
     </row>
@@ -850,25 +819,20 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>3F OPC</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>Agent初创落位</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Agent初创落位</t>
+          <t>签到→工作流→实操→Demo→看场</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>签到→工作流→实操→Demo→看场</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Agent工程师、初创团队</t>
         </is>
@@ -907,27 +871,22 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5F展示中心</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>CJ赛道企业/IP方入驻与展位</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>CJ赛道企业/IP方入驻与展位</t>
+          <t>赛道解读→IP授权→撮合→看场→建群</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>赛道解读→IP授权→一对一撮合→看场→建群</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>游戏/动漫/潮玩IP方、渠道、内容公司</t>
+          <t>游戏/动漫/潮玩IP方、渠道</t>
         </is>
       </c>
     </row>
@@ -964,25 +923,20 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>另议</t>
+          <t>另计价</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>另计价</t>
+          <t>出海服务（不在年度包内）</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>出海服务（不在年度活动包内）</t>
+          <t>另案确定</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>另案确定</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>另案确定</t>
         </is>
@@ -1021,25 +975,20 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3F培训</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>多模态团队入驻</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>多模态团队入驻</t>
+          <t>案例→实操→共创→评审→看场</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>案例→实操→共创→评审→看场</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>多模态应用团队、产品负责人</t>
         </is>
@@ -1078,27 +1027,22 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>CJ生态企业集中看场</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>CJ生态企业集中看场与洽谈</t>
+          <t>开幕→赛道分享→展洽→看场→建群</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>开幕→赛道分享→展洽→看场→建群</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>数字娱乐企业、内容工作室、渠道</t>
+          <t>数字娱乐企业、内容工作室</t>
         </is>
       </c>
     </row>
@@ -1135,25 +1079,20 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>合规型企业信任导入</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>合规型企业信任导入</t>
+          <t>治理框架→合规清单→案例→对接</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>治理框架→合规清单→案例→问答→对接</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>合规顾问、企业法务/负责人</t>
         </is>
@@ -1192,27 +1131,22 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>3F+云创基地</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>高算力企业定向看场</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>高算力企业定向看场</t>
+          <t>政策包→代金券→案例→诊断→看场</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>政策包→代金券→案例→诊断→看场</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>火山引擎、云创基地、企业技术负责人</t>
+          <t>火山引擎、云创基地、技术负责人</t>
         </is>
       </c>
     </row>
@@ -1249,25 +1183,20 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>用券企业聚集</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>用券企业聚集</t>
+          <t>三券规则→核销→案例→开户→入驻洽谈</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>三券规则→核销→案例→开户→入驻洽谈</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>券平台、云厂商、企业负责人</t>
         </is>
@@ -1306,25 +1235,20 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>会客厅/5F</t>
+          <t>另计价</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>另计价</t>
+          <t>领事到访（三部分费用之外）</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>领事到访（三部分费用之外）</t>
+          <t>另案确定</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>另案确定</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>领事及相关方（另案）</t>
         </is>
@@ -1363,25 +1287,20 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5F+3F</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>具身/机器人团队看场</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>具身/机器人团队看场</t>
+          <t>演示→讲解→场景→踩点→洽谈</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>演示→讲解→场景→踩点→洽谈</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>具身团队、高校实验室</t>
         </is>
@@ -1420,25 +1339,20 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>5F主展</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>集中签约洽谈与媒体背书</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>集中签约洽谈与媒体背书</t>
+          <t>开幕→精选路演→颁奖→洽谈</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>开幕→精选路演→颁奖→洽谈</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>投资人、链主、媒体、精选项目</t>
         </is>
@@ -1477,25 +1391,20 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3F+5F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>厂牌/工作室入驻</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>厂牌/工作室入驻</t>
+          <t>政策→制片→脚本→路演→看场</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>政策→制片→脚本→路演→看场</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>导演、厂牌、平台方</t>
         </is>
@@ -1534,25 +1443,20 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>营销科技公司看场</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>营销科技公司看场</t>
+          <t>策略→Agent→素材→复盘→转化</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>策略→Agent→素材→复盘→转化</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>投放操盘手、产品经理</t>
         </is>
@@ -1591,25 +1495,20 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5F沙龙</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>内容/AI企业导入</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>内容/AI企业导入</t>
+          <t>政策→礼包→画像→诊断→看场</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>政策→礼包→画像→诊断→看场</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>政策宣讲、服中心、企业负责人</t>
         </is>
@@ -1648,25 +1547,20 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>待认定企业带政策入驻</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>待认定企业带政策入驻</t>
+          <t>条件→材料→初筛→套餐→激励</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>条件→材料→初筛→套餐→激励</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>辅导顾问、待认定企业负责人</t>
         </is>
@@ -1705,25 +1599,20 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>获奖团队优先谈单元</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>获奖团队优先谈单元</t>
+          <t>开题→开发→路演→礼包→看场</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>开题→开发→路演→礼包→看场</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>评委、投资人、Builders</t>
         </is>
@@ -1762,27 +1651,22 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>3F+沙龙</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>成果公司/实验室落户</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>成果公司/实验室落户</t>
+          <t>成果路演→场景→承接→看单元→洽谈</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>成果路演→场景→承接→看单元→洽谈</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>复旦/同济技转、教授团队、住房政策研究中心学者</t>
+          <t>复旦/同济技转、住房政策研究中心学者</t>
         </is>
       </c>
     </row>
@@ -1819,25 +1703,20 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5F沙龙</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>研究型/模型团队</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>研究型/模型团队</t>
+          <t>议题→圆桌→围炉→问答→看场</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>议题→圆桌→围炉→问答→看场</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>学者、模型企业、投资人</t>
         </is>
@@ -1876,25 +1755,20 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>数字娱乐/内容品牌问询</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>数字娱乐/内容品牌问询</t>
+          <t>揭幕→发布→快闪→专访→招商通道</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>揭幕→发布→快闪→专访→招商通道</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>创作者、媒体、渠道、CJ内容方</t>
         </is>
@@ -1933,25 +1807,20 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>CJ供应链/周边企业展位落位</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>CJ供应链/周边企业展位落位</t>
+          <t>赛道介绍→供需对接→展位参观→报价→建群</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>赛道介绍→供需对接→展位参观→报价→建群</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>游戏周边、潮玩供应链、渠道采购</t>
         </is>
@@ -1990,25 +1859,20 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>成长型AI补位</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>成长型AI补位</t>
+          <t>政策→路演→点评→金融→看场</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>政策→路演→点评→金融→看场</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>顾问、银行、基金、企业</t>
         </is>
@@ -2047,25 +1911,20 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>优质摊主/工作室升级固定展位</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>优质摊主/工作室升级固定展位</t>
+          <t>布展→体验→交流→转正洽谈→建群</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>布展→体验→交流→转正洽谈→建群</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>内容工作室、周边品牌、达人</t>
         </is>
@@ -2104,25 +1963,20 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>IP联名/衍生品团队入驻</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>IP联名/衍生品团队入驻</t>
+          <t>IP路演→联名模式→一对一→MOU→看场</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>IP路演→联名模式→一对一→MOU→看场</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>IP方、衍生品商、渠道</t>
         </is>
@@ -2161,25 +2015,20 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>闭幕洽谈集中转化</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>闭幕洽谈集中转化</t>
+          <t>布展→预约观展→交流→闭幕洽谈</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>布展→预约观展→交流→闭幕洽谈</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>联合内容方、渠道、品牌</t>
         </is>
@@ -2218,25 +2067,20 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>5F</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>L4</t>
+          <t>旺季补位，双大会预热</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>旺季补位，双大会预热</t>
+          <t>发布→渠道→看场→年框→双会预热</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>发布→渠道→看场→年框→双会预热</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>IP方、渠道、媒体</t>
         </is>
@@ -2356,7 +2200,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>WAIC金融科技议题摘要；CJ专业观众画像</t>
+          <t>WAIC金融议题摘要；CJ专业观众画像</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2264,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>算力券/创新券口径；YOUNG立方政策包</t>
+          <t>算力券/创新券；YOUNG立方政策包</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2296,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>A/B线索抽样；ACT-001/002/006议题切片</t>
+          <t>A/B线索抽样；ACT议题切片</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>AIGC子类抽样；内容创意论坛切片</t>
+          <t>AIGC子类抽样；内容论坛切片</t>
         </is>
       </c>
     </row>
@@ -3271,9 +3115,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3298,7 +3142,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="56" customHeight="1">
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>A</t>
@@ -3306,7 +3150,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>智能体与算力训练（3F基本盘）</t>
+          <t>智能体与算力训练</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -3316,11 +3160,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>训练营负责聚人，政策/Demo Day负责转化；资源：WAIC Agent/多模态/算力/具身池抽样；重点场：A2 Agent一日营 → OPC看场</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="56" customHeight="1">
+          <t>对应WAIC：Agent·多模态·算力·具身；资源：ACT缩尺+线索抽样</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>B</t>
@@ -3328,7 +3172,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>政策与治理沙龙（进园理由）</t>
+          <t>政策与治理沙龙</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -3338,11 +3182,11 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>把补贴、资质、合规做成面对面小场；紧接算力营做券务，年底决策窗口转化；服中心现场可收件启动申报</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="56" customHeight="1">
+          <t>对应WAIC治理/券务；服中心协同兑现</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>C</t>
@@ -3350,7 +3194,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>产业与ChinaJoy对接（合并同类项）</t>
+          <t>产业与ChinaJoy对接</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -3360,11 +3204,11 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>原东莞潮玩/汕头玩具/扬州毛绒 → 统一为CJ主题；一头高校成果，一头CJ中小工作室与供应链；重点：C1 IP授权对接 / C2成果转化日</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="56" customHeight="1">
+          <t>原东莞/汕头/扬州场次合并为ChinaJoy主题内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>D</t>
@@ -3372,7 +3216,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>AI内容与ChinaJoy人气（5F引擎）</t>
+          <t>AI内容与ChinaJoy人气</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3382,11 +3226,11 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>特训供给 → 首发交易 → 市集/联展客流；与CJ创作者展区、WAIC AIGC错峰协同；重点：D4短展期联展闭幕洽谈</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="56" customHeight="1">
+          <t>对应CJ创作者经济+WAIC AIGC；与官方创作者活动错峰</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>E</t>
@@ -3394,7 +3238,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>启动月：项目推广 + 双会承接</t>
+          <t>启动月·项目推广与双会承接</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -3404,11 +3248,11 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8月四场项目推广日（中介/金融/投研/政府）；E1 WAIC成果开放交流日（≤30人精准）；E4 CJ主题日承接数字娱乐生态</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="56" customHeight="1">
+          <t>原大场改为≤30人精准场；8月=项目推广日</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>F</t>
@@ -3416,7 +3260,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>收官 · 圆桌 · 另计价事项</t>
+          <t>收官·圆桌·另计价事项</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -3426,7 +3270,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>F4 Demo Day：精选路演集中签约；F3 AGI圆桌：研究型客户深谈；F1出海 / L1领事：另议另计价，不进年度包</t>
+          <t>出海另议另计价；领事到访/挂牌另计价且分属不同性质</t>
         </is>
       </c>
     </row>
@@ -3463,144 +3307,144 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>主体运营范围</t>
+          <t>模板沿用</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>上海市云计算创新基地（国家级孵化器）</t>
+          <t>扉页实景封面、米白底#F8F7F3、金色点缀、五章目录结构、主题开场实景页</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>学术支持</t>
+          <t>主体运营范围</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>复旦大学住房政策研究中心</t>
+          <t>上海市云计算创新基地（国家级孵化器）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>载体支持</t>
+          <t>学术支持</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>杨浦区科技企业联合会、科技企业服务中心</t>
+          <t>复旦大学住房政策研究中心</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>执行带客</t>
+          <t>载体支持</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>同浦汇</t>
+          <t>杨浦区科技企业联合会、科技企业服务中心</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>执行带客</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>园区负责销售部分</t>
+          <t>同浦汇</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>人数</t>
+          <t>销售</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>每场≤30人；全年约600人次+</t>
+          <t>园区负责销售部分</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>负责人</t>
+          <t>人数</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>每场≤30人；全年约600人次+</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>双会</t>
+          <t>负责人</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>WAIC→3F；ChinaJoy→5F；具身/AIGC叠加</t>
+          <t>约50%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>出海/领事</t>
+          <t>双会</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>另议另计价；到访≠挂牌</t>
+          <t>WAIC→3F；ChinaJoy→5F；具身/AIGC叠加</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>租金</t>
+          <t>出海/领事</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>3.3元/㎡/天；不做对赌与必要性要求；免租期1–3个月面议</t>
+          <t>另议另计价；到访≠挂牌</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>付款</t>
+          <t>租金</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>签约后7日50%；四季各10%；年终10%</t>
+          <t>3.3元/㎡/天；不做对赌；免租期1–3个月面议</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>合并原则</t>
+          <t>付款</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>结构以年度方案PPT为主；场次与资源以双会修订版并入；删除冲突旧口径</t>
+          <t>签约后7日50%；四季各10%；年终10%</t>
         </is>
       </c>
     </row>

--- a/proposal/创智汇年度活动运营方案-融合版.xlsx
+++ b/proposal/创智汇年度活动运营方案-融合版.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-活动概况" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-定义核资源导入" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-六大主题" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-主体口径与模板说明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-主体口径" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -48,12 +48,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A5F"/>
+        <fgColor rgb="003A206E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F0EA"/>
+        <fgColor rgb="00F3F0FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,16 +67,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="004A3C7C"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="004A3C7C"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="004A3C7C"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="004A3C7C"/>
       </bottom>
     </border>
   </borders>
@@ -3307,12 +3307,12 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>模板沿用</t>
+          <t>视觉</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>扉页实景封面、米白底#F8F7F3、金色点缀、五章目录结构、主题开场实景页</t>
+          <t>皇家紫金主题（深紫渐变+蓝紫点缀+香槟金）</t>
         </is>
       </c>
     </row>

--- a/proposal/创智汇年度活动运营方案-融合版.xlsx
+++ b/proposal/创智汇年度活动运营方案-融合版.xlsx
@@ -3285,7 +3285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3307,144 +3307,180 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>视觉</t>
+          <t>定稿说明</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>皇家紫金主题（深紫渐变+蓝紫点缀+香槟金）</t>
+          <t>多版优胜劣汰合并；紫金主题；Excel0804场次为准</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>主体运营范围</t>
+          <t>视觉</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>上海市云计算创新基地（国家级孵化器）</t>
+          <t>皇家紫金主题（深紫渐变+蓝紫点缀+香槟金）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>学术支持</t>
+          <t>主体运营范围</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>复旦大学住房政策研究中心</t>
+          <t>上海市云计算创新基地（国家级孵化器）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>载体支持</t>
+          <t>学术支持</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>杨浦区科技企业联合会、科技企业服务中心</t>
+          <t>复旦大学住房政策研究中心</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>执行带客</t>
+          <t>载体支持</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>同浦汇</t>
+          <t>杨浦区科技企业联合会、科技企业服务中心</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>执行带客</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>园区负责销售部分</t>
+          <t>同浦汇</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>人数</t>
+          <t>销售</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>每场≤30人；全年约600人次+</t>
+          <t>园区负责销售部分</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>负责人</t>
+          <t>人数</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>每场≤30人；全年约600人次+</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>双会</t>
+          <t>负责人</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>WAIC→3F；ChinaJoy→5F；具身/AIGC叠加</t>
+          <t>约50%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>出海/领事</t>
+          <t>双会</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>另议另计价；到访≠挂牌</t>
+          <t>WAIC→3F；ChinaJoy→5F；具身/AIGC叠加</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>租金</t>
+          <t>最新时点</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>3.3元/㎡/天；不做对赌；免租期1–3个月面议</t>
+          <t>2026.08：WAIC已闭幕、ChinaJoy刚结束，进入承接期</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>出海/领事</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>另议另计价；到访≠挂牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>租金</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>3.3元/㎡/天；不做对赌；免租期1–3个月面议</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>付款</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>签约后7日50%；四季各10%；年终10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>剔除</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>关联度核验表、千人级承诺、潮玩产业集群旧场、租赁对赌主叙事</t>
         </is>
       </c>
     </row>

--- a/proposal/创智汇年度活动运营方案-融合版.xlsx
+++ b/proposal/创智汇年度活动运营方案-融合版.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -3285,7 +3285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3307,180 +3307,144 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定稿说明</t>
+          <t>视觉</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>多版优胜劣汰合并；紫金主题；Excel0804场次为准</t>
+          <t>皇家紫金主题（深紫渐变+蓝紫点缀+香槟金）</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>视觉</t>
+          <t>主体运营范围</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>皇家紫金主题（深紫渐变+蓝紫点缀+香槟金）</t>
+          <t>上海市云计算创新基地（国家级孵化器）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>主体运营范围</t>
+          <t>学术支持</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>上海市云计算创新基地（国家级孵化器）</t>
+          <t>复旦大学住房政策研究中心</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>学术支持</t>
+          <t>载体支持</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>复旦大学住房政策研究中心</t>
+          <t>杨浦区科技企业联合会、科技企业服务中心</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>载体支持</t>
+          <t>执行带客</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>杨浦区科技企业联合会、科技企业服务中心</t>
+          <t>同浦汇</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>执行带客</t>
+          <t>销售</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>同浦汇</t>
+          <t>园区负责销售部分</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>人数</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>园区负责销售部分</t>
+          <t>每场≤30人；全年约600人次+</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>人数</t>
+          <t>负责人</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>每场≤30人；全年约600人次+</t>
+          <t>≤30%</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>负责人</t>
+          <t>双会</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>WAIC→3F；ChinaJoy→5F；具身/AIGC叠加</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>双会</t>
+          <t>出海/领事</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>WAIC→3F；ChinaJoy→5F；具身/AIGC叠加</t>
+          <t>另议另计价；到访≠挂牌</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>最新时点</t>
+          <t>租金</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026.08：WAIC已闭幕、ChinaJoy刚结束，进入承接期</t>
+          <t>3.3元/㎡/天；不做对赌；免租期1–3个月面议</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>出海/领事</t>
+          <t>付款</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>另议另计价；到访≠挂牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>租金</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>3.3元/㎡/天；不做对赌；免租期1–3个月面议</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>付款</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
           <t>签约后7日50%；四季各10%；年终10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>剔除</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>关联度核验表、千人级承诺、潮玩产业集群旧场、租赁对赌主叙事</t>
         </is>
       </c>
     </row>
